--- a/e2e/expectedData/Non_Regular_Salary_Hometrip_Q1.xlsx
+++ b/e2e/expectedData/Non_Regular_Salary_Hometrip_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -59,39 +59,48 @@
     <t>MAR</t>
   </si>
   <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>550,00</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>1.100,00</t>
+  </si>
+  <si>
+    <t>110,00</t>
+  </si>
+  <si>
     <t>CELIA MARIA REGO DE FATIMA</t>
   </si>
   <si>
     <t>IV</t>
   </si>
   <si>
-    <t>Expat</t>
-  </si>
-  <si>
-    <t>550,00</t>
+    <t>Local</t>
   </si>
   <si>
     <t>1.650,00</t>
   </si>
   <si>
+    <t>115,00</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
     <t>165,00</t>
   </si>
   <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>1.100,00</t>
-  </si>
-  <si>
-    <t>110,00</t>
-  </si>
-  <si>
     <t>HERU YULIANTO</t>
   </si>
   <si>
@@ -101,21 +110,18 @@
     <t>Homestaff</t>
   </si>
   <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>300,00</t>
   </si>
   <si>
     <t>RIMBUN SIBURIAN</t>
   </si>
   <si>
-    <t>100,00</t>
-  </si>
-  <si>
-    <t>300,00</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
     <t>SYALDY KHARISMA ANANDA</t>
   </si>
   <si>
@@ -131,7 +137,10 @@
     <t>6.300,00</t>
   </si>
   <si>
-    <t>DILI, 26 August 2026</t>
+    <t>500,00</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -648,7 +657,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="3">
-        <v>92003</v>
+        <v>24016</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>14</v>
@@ -667,27 +676,27 @@
         <v>17</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="3">
-        <v>24016</v>
+        <v>92003</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
@@ -697,27 +706,27 @@
         <v>17</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="3">
-        <v>74003</v>
+        <v>95008</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
@@ -727,27 +736,27 @@
         <v>17</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3">
-        <v>95008</v>
+        <v>74003</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
@@ -757,21 +766,21 @@
         <v>17</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="3">
-        <v>81010</v>
+        <v>26013</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>15</v>
@@ -781,49 +790,49 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="3">
-        <v>26013</v>
+        <v>81010</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -831,34 +840,34 @@
         <v>91015</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -868,10 +877,10 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -879,20 +888,20 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -901,11 +910,11 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E18"/>
       <c r="G18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="37.5">
@@ -915,20 +924,20 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E20"/>
       <c r="G20" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E21"/>
       <c r="G21" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/e2e/expectedData/Non_Regular_Salary_Hometrip_Q1.xlsx
+++ b/e2e/expectedData/Non_Regular_Salary_Hometrip_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -65,39 +65,42 @@
     <t>VI</t>
   </si>
   <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>550,00</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>1.100,00</t>
+  </si>
+  <si>
+    <t>110,00</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>1.650,00</t>
+  </si>
+  <si>
+    <t>115,00</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
     <t>Expat</t>
   </si>
   <si>
-    <t>550,00</t>
-  </si>
-  <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>1.100,00</t>
-  </si>
-  <si>
-    <t>110,00</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>1.650,00</t>
-  </si>
-  <si>
-    <t>115,00</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
     <t>165,00</t>
   </si>
   <si>
@@ -140,7 +143,7 @@
     <t>500,00</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -726,7 +729,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
@@ -742,7 +745,7 @@
         <v>24</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -750,13 +753,13 @@
         <v>74003</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
@@ -780,26 +783,26 @@
         <v>26013</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>18</v>
@@ -810,7 +813,7 @@
         <v>81010</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
@@ -820,16 +823,16 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>18</v>
@@ -840,26 +843,26 @@
         <v>91015</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>18</v>
@@ -867,7 +870,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -877,10 +880,10 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -888,20 +891,20 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -910,11 +913,11 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E18"/>
       <c r="G18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="37.5">
@@ -924,20 +927,20 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20"/>
       <c r="G20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21"/>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
